--- a/salidas/empresas/SPGI.xlsx
+++ b/salidas/empresas/SPGI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>33.68463516235352</v>
+        <v>33.68464660644531</v>
       </c>
       <c r="C2" t="n">
         <v>48.28760528564453</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>35.15526580810547</v>
+        <v>35.15530014038086</v>
       </c>
       <c r="C3" t="n">
         <v>50.22705841064453</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>38.15497207641602</v>
+        <v>38.15498352050781</v>
       </c>
       <c r="C4" t="n">
         <v>54.51277160644531</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>34.29087066650391</v>
+        <v>34.29086303710938</v>
       </c>
       <c r="C6" t="n">
         <v>48.81740951538086</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.38042449951172</v>
+        <v>33.38042831420898</v>
       </c>
       <c r="C7" t="n">
         <v>47.52128601074219</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>37.41426086425781</v>
+        <v>37.41425704956055</v>
       </c>
       <c r="C8" t="n">
         <v>53.26395416259766</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>37.27594757080078</v>
+        <v>37.27594375610352</v>
       </c>
       <c r="C9" t="n">
         <v>52.89498519897461</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>42.78300857543945</v>
+        <v>42.78299713134766</v>
       </c>
       <c r="C11" t="n">
         <v>60.70955657958984</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>45.47502517700195</v>
+        <v>45.47502136230469</v>
       </c>
       <c r="C13" t="n">
         <v>64.35193634033203</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>44.84658813476562</v>
+        <v>44.84660339355469</v>
       </c>
       <c r="C14" t="n">
         <v>63.46263122558594</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>43.29112243652344</v>
+        <v>43.29111480712891</v>
       </c>
       <c r="C15" t="n">
         <v>61.07852554321289</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.16458511352539</v>
+        <v>42.16456985473633</v>
       </c>
       <c r="C16" t="n">
         <v>59.48912048339844</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>43.94155502319336</v>
+        <v>43.94157028198242</v>
       </c>
       <c r="C17" t="n">
         <v>61.9962158203125</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>47.28409576416016</v>
+        <v>47.28409194946289</v>
       </c>
       <c r="C18" t="n">
         <v>66.51844787597656</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>45.78440093994141</v>
+        <v>45.78440856933594</v>
       </c>
       <c r="C19" t="n">
         <v>64.40870666503906</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>40.68678665161133</v>
+        <v>40.68678283691406</v>
       </c>
       <c r="C20" t="n">
         <v>57.23746490478516</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>34.07351684570312</v>
+        <v>34.07352447509766</v>
       </c>
       <c r="C21" t="n">
         <v>47.73888397216797</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>34.37738800048828</v>
+        <v>34.37738418579102</v>
       </c>
       <c r="C22" t="n">
         <v>48.16461563110352</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>33.78990173339844</v>
+        <v>33.7899055480957</v>
       </c>
       <c r="C23" t="n">
         <v>47.34153366088867</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>29.71495819091797</v>
+        <v>29.71497917175293</v>
       </c>
       <c r="C25" t="n">
         <v>41.44749450683594</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.00277709960938</v>
+        <v>29.00277137756348</v>
       </c>
       <c r="C26" t="n">
         <v>40.45411682128906</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>27.91092681884766</v>
+        <v>27.91091346740723</v>
       </c>
       <c r="C27" t="n">
         <v>38.72280120849609</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>25.19687461853027</v>
+        <v>25.19687652587891</v>
       </c>
       <c r="C28" t="n">
         <v>34.95742797851562</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>27.95183181762695</v>
+        <v>27.95182418823242</v>
       </c>
       <c r="C29" t="n">
         <v>38.77956390380859</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>28.4456615447998</v>
+        <v>28.44564247131348</v>
       </c>
       <c r="C30" t="n">
         <v>39.25260162353516</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>27.50637245178223</v>
+        <v>27.50636672973633</v>
       </c>
       <c r="C31" t="n">
         <v>37.95648193359375</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.88345527648926</v>
+        <v>27.88345718383789</v>
       </c>
       <c r="C32" t="n">
         <v>38.47682189941406</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>29.52638626098633</v>
+        <v>29.52638244628906</v>
       </c>
       <c r="C33" t="n">
         <v>40.52980041503906</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>21.7863941192627</v>
+        <v>21.78639030456543</v>
       </c>
       <c r="C34" t="n">
         <v>29.90539360046387</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>18.51257514953613</v>
+        <v>18.51258087158203</v>
       </c>
       <c r="C35" t="n">
         <v>25.41154289245605</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.43697357177734</v>
+        <v>17.43697738647461</v>
       </c>
       <c r="C36" t="n">
         <v>23.65184593200684</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.17453956604004</v>
+        <v>16.17453765869141</v>
       </c>
       <c r="C37" t="n">
         <v>21.93945121765137</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>15.33756256103516</v>
+        <v>15.33755970001221</v>
       </c>
       <c r="C38" t="n">
         <v>20.80416297912598</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>13.90916347503662</v>
+        <v>13.90916442871094</v>
       </c>
       <c r="C39" t="n">
         <v>18.66603660583496</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>16.12277984619141</v>
+        <v>16.12278175354004</v>
       </c>
       <c r="C40" t="n">
         <v>21.6367073059082</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.25499725341797</v>
+        <v>21.2549991607666</v>
       </c>
       <c r="C41" t="n">
         <v>28.52412414550781</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.36920928955078</v>
+        <v>21.36922264099121</v>
       </c>
       <c r="C42" t="n">
         <v>28.46735954284668</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.3834228515625</v>
+        <v>21.38342094421387</v>
       </c>
       <c r="C43" t="n">
         <v>28.48628234863281</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.26404762268066</v>
+        <v>22.2640323638916</v>
       </c>
       <c r="C44" t="n">
         <v>29.6594123840332</v>
@@ -1305,7 +1317,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>17.99026489257812</v>
+        <v>17.99027442932129</v>
       </c>
       <c r="C46" t="n">
         <v>23.78429412841797</v>
@@ -1355,7 +1367,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.59626960754395</v>
+        <v>21.59627342224121</v>
       </c>
       <c r="C48" t="n">
         <v>28.3443717956543</v>
@@ -1405,7 +1417,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>25.55366897583008</v>
+        <v>25.55367660522461</v>
       </c>
       <c r="C50" t="n">
         <v>33.53831481933594</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.81770133972168</v>
+        <v>24.81769561767578</v>
       </c>
       <c r="C51" t="n">
         <v>32.3557243347168</v>
@@ -1480,7 +1492,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>24.46938133239746</v>
+        <v>24.46938514709473</v>
       </c>
       <c r="C53" t="n">
         <v>31.90160751342773</v>
@@ -1530,7 +1542,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>20.59049797058105</v>
+        <v>20.59049415588379</v>
       </c>
       <c r="C55" t="n">
         <v>26.62251663208008</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>22.45637130737305</v>
+        <v>22.45637893676758</v>
       </c>
       <c r="C56" t="n">
         <v>29.03500556945801</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>20.40332221984863</v>
+        <v>20.4033260345459</v>
       </c>
       <c r="C57" t="n">
         <v>26.15893936157227</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>24.39543533325195</v>
+        <v>24.39543342590332</v>
       </c>
       <c r="C58" t="n">
         <v>31.27720069885254</v>
@@ -1655,7 +1667,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>25.62263870239258</v>
+        <v>25.62264060974121</v>
       </c>
       <c r="C60" t="n">
         <v>32.63008499145508</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>27.04900932312012</v>
+        <v>27.04901313781738</v>
       </c>
       <c r="C61" t="n">
         <v>34.44654846191406</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>28.95826721191406</v>
+        <v>28.95825004577637</v>
       </c>
       <c r="C62" t="n">
         <v>36.87795639038086</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>28.9214973449707</v>
+        <v>28.92151641845703</v>
       </c>
       <c r="C63" t="n">
         <v>36.59413528442383</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>29.4598560333252</v>
+        <v>29.45984840393066</v>
       </c>
       <c r="C64" t="n">
         <v>37.27530670166016</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>30.25991058349609</v>
+        <v>30.25991439819336</v>
       </c>
       <c r="C65" t="n">
         <v>38.28760528564453</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>31.94394493103027</v>
+        <v>31.94393920898438</v>
       </c>
       <c r="C66" t="n">
         <v>40.17975234985352</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>31.52273750305176</v>
+        <v>31.52274894714355</v>
       </c>
       <c r="C67" t="n">
         <v>39.64995193481445</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>31.28957366943359</v>
+        <v>31.28958511352539</v>
       </c>
       <c r="C68" t="n">
         <v>39.35667037963867</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.8791675567627</v>
+        <v>31.87916564941406</v>
       </c>
       <c r="C69" t="n">
         <v>39.83916854858398</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>31.03885459899902</v>
+        <v>31.03883934020996</v>
       </c>
       <c r="C70" t="n">
         <v>38.78902435302734</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.17441177368164</v>
+        <v>32.17441558837891</v>
       </c>
       <c r="C71" t="n">
         <v>40.20813751220703</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>32.51183700561523</v>
+        <v>32.51186752319336</v>
       </c>
       <c r="C72" t="n">
         <v>40.3973503112793</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>34.240234375</v>
+        <v>34.24024200439453</v>
       </c>
       <c r="C73" t="n">
         <v>42.54493713378906</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>35.02449417114258</v>
+        <v>35.02447128295898</v>
       </c>
       <c r="C74" t="n">
         <v>43.51939392089844</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>35.63434600830078</v>
+        <v>35.63434219360352</v>
       </c>
       <c r="C75" t="n">
         <v>44.0302734375</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>37.11208343505859</v>
+        <v>37.11208724975586</v>
       </c>
       <c r="C76" t="n">
         <v>45.85619735717773</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>37.64805603027344</v>
+        <v>37.64806747436523</v>
       </c>
       <c r="C77" t="n">
         <v>46.51844787597656</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>33.40462112426758</v>
+        <v>33.40462493896484</v>
       </c>
       <c r="C78" t="n">
         <v>41.04067993164062</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>34.65209579467773</v>
+        <v>34.652099609375</v>
       </c>
       <c r="C79" t="n">
         <v>42.57332229614258</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>36.16139602661133</v>
+        <v>36.16138458251953</v>
       </c>
       <c r="C80" t="n">
         <v>44.4276237487793</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>39.63049697875977</v>
+        <v>39.63051223754883</v>
       </c>
       <c r="C81" t="n">
         <v>48.4389762878418</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>42.25447845458984</v>
+        <v>42.25448226928711</v>
       </c>
       <c r="C82" t="n">
         <v>51.64616775512695</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>42.78855514526367</v>
+        <v>42.78854751586914</v>
       </c>
       <c r="C83" t="n">
         <v>52.29895782470703</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>41.31172943115234</v>
+        <v>41.31171798706055</v>
       </c>
       <c r="C84" t="n">
         <v>50.24597930908203</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>44.55250549316406</v>
+        <v>44.5525016784668</v>
       </c>
       <c r="C85" t="n">
         <v>51.72185516357422</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>46.87506103515625</v>
+        <v>46.87506484985352</v>
       </c>
       <c r="C86" t="n">
         <v>54.41816329956055</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>38.16830444335938</v>
+        <v>38.1683235168457</v>
       </c>
       <c r="C87" t="n">
         <v>44.03973388671875</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>42.70259857177734</v>
+        <v>42.70259094238281</v>
       </c>
       <c r="C88" t="n">
         <v>49.27152252197266</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>44.36708068847656</v>
+        <v>44.3670768737793</v>
       </c>
       <c r="C89" t="n">
         <v>51.19205474853516</v>
@@ -2538,7 +2550,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>43.83992004394531</v>
+        <v>43.83991622924805</v>
       </c>
       <c r="C91" t="n">
         <v>50.3216667175293</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>50.9858512878418</v>
+        <v>50.98586273193359</v>
       </c>
       <c r="C92" t="n">
         <v>58.52412414550781</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>48.33486557006836</v>
+        <v>48.33486938476562</v>
       </c>
       <c r="C93" t="n">
         <v>55.22232818603516</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>54.31360244750977</v>
+        <v>54.3135986328125</v>
       </c>
       <c r="C94" t="n">
         <v>62.052978515625</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>57.7004280090332</v>
+        <v>57.7004508972168</v>
       </c>
       <c r="C95" t="n">
         <v>65.92242431640625</v>
@@ -2712,7 +2724,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>65.00244903564453</v>
+        <v>65.00246429443359</v>
       </c>
       <c r="C97" t="n">
         <v>73.98297119140625</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>63.20698165893555</v>
+        <v>63.20700454711914</v>
       </c>
       <c r="C98" t="n">
         <v>71.939453125</v>
@@ -2799,7 +2811,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>63.66115570068359</v>
+        <v>63.66114807128906</v>
       </c>
       <c r="C100" t="n">
         <v>72.18543243408203</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>61.68377304077148</v>
+        <v>61.68376922607422</v>
       </c>
       <c r="C101" t="n">
         <v>69.9432373046875</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>68.4830322265625</v>
+        <v>68.48304748535156</v>
       </c>
       <c r="C102" t="n">
         <v>77.36045074462891</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>69.53830718994141</v>
+        <v>69.53831481933594</v>
       </c>
       <c r="C103" t="n">
         <v>78.55250549316406</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>67.18495178222656</v>
+        <v>67.18492126464844</v>
       </c>
       <c r="C104" t="n">
         <v>75.89404296875</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>68.20451354980469</v>
+        <v>68.20455932617188</v>
       </c>
       <c r="C105" t="n">
         <v>76.75496673583984</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.99556732177734</v>
+        <v>70.99560546875</v>
       </c>
       <c r="C106" t="n">
         <v>79.89593505859375</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>76.06490325927734</v>
+        <v>76.06491088867188</v>
       </c>
       <c r="C107" t="n">
         <v>85.60075378417969</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>78.83039093017578</v>
+        <v>78.83036804199219</v>
       </c>
       <c r="C108" t="n">
         <v>88.42005920410156</v>
@@ -3089,7 +3101,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>75.43965148925781</v>
+        <v>75.43965911865234</v>
       </c>
       <c r="C110" t="n">
         <v>84.61683654785156</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>87.23656463623047</v>
+        <v>87.23654937744141</v>
       </c>
       <c r="C111" t="n">
         <v>97.54020690917969</v>
@@ -3174,7 +3186,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3201,11 +3213,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>88.25189971923828</v>
+        <v>88.25194549560547</v>
       </c>
       <c r="C113" t="n">
         <v>98.67549896240234</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>88.05846405029297</v>
+        <v>88.05843353271484</v>
       </c>
       <c r="C114" t="n">
         <v>98.15515899658203</v>
@@ -3255,11 +3267,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>85.257568359375</v>
+        <v>85.25759124755859</v>
       </c>
       <c r="C115" t="n">
         <v>95.03311157226562</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>86.36093902587891</v>
+        <v>86.36094665527344</v>
       </c>
       <c r="C116" t="n">
         <v>96.26300811767578</v>
@@ -3309,11 +3321,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>82.60340118408203</v>
+        <v>82.60338592529297</v>
       </c>
       <c r="C117" t="n">
         <v>91.75969696044922</v>
@@ -3336,11 +3348,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>73.66941070556641</v>
+        <v>73.66935729980469</v>
       </c>
       <c r="C118" t="n">
         <v>81.83538055419922</v>
@@ -3363,11 +3375,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>78.89862823486328</v>
+        <v>78.89864349365234</v>
       </c>
       <c r="C119" t="n">
         <v>87.64427947998047</v>
@@ -3390,11 +3402,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>82.44131469726562</v>
+        <v>82.44129180908203</v>
       </c>
       <c r="C120" t="n">
         <v>91.26773834228516</v>
@@ -3419,11 +3431,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>84.24448394775391</v>
+        <v>84.24446868896484</v>
       </c>
       <c r="C121" t="n">
         <v>93.26395416259766</v>
@@ -3448,11 +3460,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>72.65639495849609</v>
+        <v>72.65638732910156</v>
       </c>
       <c r="C122" t="n">
         <v>80.43519592285156</v>
@@ -3477,11 +3489,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>76.99990081787109</v>
+        <v>76.99989318847656</v>
       </c>
       <c r="C123" t="n">
         <v>84.90066528320312</v>
@@ -3506,11 +3518,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>84.92814636230469</v>
+        <v>84.92810821533203</v>
       </c>
       <c r="C124" t="n">
         <v>93.64238739013672</v>
@@ -3535,11 +3547,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>91.68086242675781</v>
+        <v>91.68083953857422</v>
       </c>
       <c r="C125" t="n">
         <v>101.0879821777344</v>
@@ -3564,11 +3576,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>96.25508880615234</v>
+        <v>96.25505828857422</v>
       </c>
       <c r="C126" t="n">
         <v>105.7805099487305</v>
@@ -3593,11 +3605,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>92.33805847167969</v>
+        <v>92.33805084228516</v>
       </c>
       <c r="C127" t="n">
         <v>101.4758758544922</v>
@@ -3622,11 +3634,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>105.1996154785156</v>
+        <v>105.1996231079102</v>
       </c>
       <c r="C128" t="n">
         <v>115.6102142333984</v>
@@ -3651,11 +3663,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>106.6698684692383</v>
+        <v>106.6698455810547</v>
       </c>
       <c r="C129" t="n">
         <v>116.8779525756836</v>
@@ -3680,7 +3692,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3709,7 +3721,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>103.0482635498047</v>
+        <v>103.0482559204102</v>
       </c>
       <c r="C132" t="n">
         <v>112.5733184814453</v>
@@ -3767,11 +3779,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>93.13226318359375</v>
+        <v>93.13227081298828</v>
       </c>
       <c r="C133" t="n">
         <v>101.7407760620117</v>
@@ -3796,11 +3808,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>104.0788116455078</v>
+        <v>104.0788421630859</v>
       </c>
       <c r="C134" t="n">
         <v>113.6991500854492</v>
@@ -3825,11 +3837,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>112.4768600463867</v>
+        <v>112.4768753051758</v>
       </c>
       <c r="C135" t="n">
         <v>122.4881744384766</v>
@@ -3854,11 +3866,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>113.580192565918</v>
+        <v>113.5801696777344</v>
       </c>
       <c r="C136" t="n">
         <v>123.6896896362305</v>
@@ -3883,11 +3895,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>116.5773391723633</v>
+        <v>116.5773696899414</v>
       </c>
       <c r="C137" t="n">
         <v>126.9536437988281</v>
@@ -3912,11 +3924,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>124.4350967407227</v>
+        <v>124.4351272583008</v>
       </c>
       <c r="C138" t="n">
         <v>135.1087951660156</v>
@@ -3941,11 +3953,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>127.2059555053711</v>
+        <v>127.2059097290039</v>
       </c>
       <c r="C139" t="n">
         <v>138.1173095703125</v>
@@ -3970,11 +3982,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>133.828125</v>
+        <v>133.8280944824219</v>
       </c>
       <c r="C140" t="n">
         <v>145.3074798583984</v>
@@ -3999,11 +4011,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>134.8383026123047</v>
+        <v>134.8382568359375</v>
       </c>
       <c r="C141" t="n">
         <v>146.007568359375</v>
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>136.5682525634766</v>
+        <v>136.5682678222656</v>
       </c>
       <c r="C142" t="n">
         <v>147.8807983398438</v>
@@ -4057,7 +4069,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4086,11 +4098,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>144.9420776367188</v>
+        <v>144.9421234130859</v>
       </c>
       <c r="C144" t="n">
         <v>156.5562896728516</v>
@@ -4115,11 +4127,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>148.3756256103516</v>
+        <v>148.3755798339844</v>
       </c>
       <c r="C145" t="n">
         <v>160.2649078369141</v>
@@ -4144,11 +4156,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>158.62353515625</v>
+        <v>158.6234893798828</v>
       </c>
       <c r="C146" t="n">
         <v>171.3339691162109</v>
@@ -4173,7 +4185,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4202,11 +4214,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>167.7939758300781</v>
+        <v>167.7939910888672</v>
       </c>
       <c r="C148" t="n">
         <v>180.7568664550781</v>
@@ -4231,11 +4243,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>165.633544921875</v>
+        <v>165.6335601806641</v>
       </c>
       <c r="C149" t="n">
         <v>178.4295196533203</v>
@@ -4260,11 +4272,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>173.8848571777344</v>
+        <v>173.8848876953125</v>
       </c>
       <c r="C150" t="n">
         <v>186.8495788574219</v>
@@ -4289,11 +4301,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>179.5108337402344</v>
+        <v>179.5108032226562</v>
       </c>
       <c r="C151" t="n">
         <v>192.8949890136719</v>
@@ -4318,11 +4330,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>176.4733428955078</v>
+        <v>176.4733581542969</v>
       </c>
       <c r="C152" t="n">
         <v>189.6310272216797</v>
@@ -4347,11 +4359,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>182.7434539794922</v>
+        <v>182.7434387207031</v>
       </c>
       <c r="C153" t="n">
         <v>195.8845825195312</v>
@@ -4376,7 +4388,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4405,11 +4417,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>160.9165802001953</v>
+        <v>160.9166412353516</v>
       </c>
       <c r="C155" t="n">
         <v>172.4881744384766</v>
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>161.8493957519531</v>
+        <v>161.8492889404297</v>
       </c>
       <c r="C156" t="n">
         <v>172.9990539550781</v>
@@ -4463,11 +4475,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>150.4138793945312</v>
+        <v>150.413818359375</v>
       </c>
       <c r="C157" t="n">
         <v>160.7757873535156</v>
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>169.6294250488281</v>
+        <v>169.6293792724609</v>
       </c>
       <c r="C158" t="n">
         <v>181.3150482177734</v>
@@ -4521,11 +4533,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>177.8496398925781</v>
+        <v>177.849609375</v>
       </c>
       <c r="C159" t="n">
         <v>189.5648040771484</v>
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>186.8854370117188</v>
+        <v>186.8854064941406</v>
       </c>
       <c r="C160" t="n">
         <v>199.1958312988281</v>
@@ -4579,11 +4591,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>195.859130859375</v>
+        <v>195.8591613769531</v>
       </c>
       <c r="C161" t="n">
         <v>208.7606353759766</v>
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>190.3473815917969</v>
+        <v>190.3473968505859</v>
       </c>
       <c r="C162" t="n">
         <v>202.3462677001953</v>
@@ -4637,7 +4649,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4666,11 +4678,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>217.9988403320312</v>
+        <v>217.9988555908203</v>
       </c>
       <c r="C164" t="n">
         <v>231.7407684326172</v>
@@ -4695,11 +4707,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>232.0766448974609</v>
+        <v>232.0766296386719</v>
       </c>
       <c r="C165" t="n">
         <v>246.158935546875</v>
@@ -4724,7 +4736,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>230.1143798828125</v>
+        <v>230.1143646240234</v>
       </c>
       <c r="C167" t="n">
         <v>244.0775756835938</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>236.5631713867188</v>
+        <v>236.5632171630859</v>
       </c>
       <c r="C168" t="n">
         <v>250.3784332275391</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>244.0716857910156</v>
+        <v>244.0717163085938</v>
       </c>
       <c r="C169" t="n">
         <v>258.325439453125</v>
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>262.5569763183594</v>
+        <v>262.5569152832031</v>
       </c>
       <c r="C170" t="n">
         <v>277.8902587890625</v>
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>238.2381439208984</v>
+        <v>238.2382049560547</v>
       </c>
       <c r="C171" t="n">
         <v>251.5704803466797</v>
@@ -4898,7 +4910,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4927,7 +4939,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4956,7 +4968,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>295.8283081054688</v>
+        <v>295.828369140625</v>
       </c>
       <c r="C175" t="n">
         <v>311.71240234375</v>
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>314.4769592285156</v>
+        <v>314.4770202636719</v>
       </c>
       <c r="C176" t="n">
         <v>331.3623352050781</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>329.6089172363281</v>
+        <v>329.60888671875</v>
       </c>
       <c r="C177" t="n">
         <v>346.6603698730469</v>
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>324.3735046386719</v>
+        <v>324.3735961914062</v>
       </c>
       <c r="C178" t="n">
         <v>341.1542053222656</v>
@@ -5101,7 +5113,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5130,7 +5142,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5159,11 +5171,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>296.2942199707031</v>
+        <v>296.2940673828125</v>
       </c>
       <c r="C181" t="n">
         <v>311.0028381347656</v>
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>285.7215270996094</v>
+        <v>285.7215576171875</v>
       </c>
       <c r="C182" t="n">
         <v>299.9053955078125</v>
@@ -5217,11 +5229,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>297.5494079589844</v>
+        <v>297.5494689941406</v>
       </c>
       <c r="C183" t="n">
         <v>311.598876953125</v>
@@ -5246,7 +5258,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>352.6849670410156</v>
+        <v>352.6848754882812</v>
       </c>
       <c r="C185" t="n">
         <v>369.3377380371094</v>
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>343.5174560546875</v>
+        <v>343.5174865722656</v>
       </c>
       <c r="C186" t="n">
         <v>359.0066223144531</v>
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>371.5622253417969</v>
+        <v>371.5623168945312</v>
       </c>
       <c r="C187" t="n">
         <v>388.3159790039062</v>
@@ -5362,11 +5374,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>388.101318359375</v>
+        <v>388.1012573242188</v>
       </c>
       <c r="C188" t="n">
         <v>405.6007690429688</v>
@@ -5391,7 +5403,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>385.3120727539062</v>
+        <v>385.3121337890625</v>
       </c>
       <c r="C190" t="n">
         <v>401.977294921875</v>
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>429.9927368164062</v>
+        <v>429.9927978515625</v>
       </c>
       <c r="C191" t="n">
         <v>448.5903625488281</v>
@@ -5478,11 +5490,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>413.9748840332031</v>
+        <v>413.9749450683594</v>
       </c>
       <c r="C192" t="n">
         <v>431.1542053222656</v>
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>428.6906433105469</v>
+        <v>428.6906127929688</v>
       </c>
       <c r="C193" t="n">
         <v>446.4805908203125</v>
@@ -5536,11 +5548,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>377.1765747070312</v>
+        <v>377.1765441894531</v>
       </c>
       <c r="C194" t="n">
         <v>392.8287658691406</v>
@@ -5565,11 +5577,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>341.9360046386719</v>
+        <v>341.9359741210938</v>
       </c>
       <c r="C195" t="n">
         <v>355.4399108886719</v>
@@ -5594,7 +5606,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5623,7 +5635,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>318.8519897460938</v>
+        <v>318.8519592285156</v>
       </c>
       <c r="C198" t="n">
         <v>330.6338806152344</v>
@@ -5681,11 +5693,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>307.5204467773438</v>
+        <v>307.5204162597656</v>
       </c>
       <c r="C199" t="n">
         <v>318.8836364746094</v>
@@ -5710,11 +5722,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>343.8963317871094</v>
+        <v>343.8963012695312</v>
       </c>
       <c r="C200" t="n">
         <v>356.6036071777344</v>
@@ -5739,11 +5751,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>322.0439453125</v>
+        <v>322.0439147949219</v>
       </c>
       <c r="C201" t="n">
         <v>333.1882629394531</v>
@@ -5768,11 +5780,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>279.2212219238281</v>
+        <v>279.22119140625</v>
       </c>
       <c r="C202" t="n">
         <v>288.8836364746094</v>
@@ -5797,11 +5809,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>293.7606201171875</v>
+        <v>293.7606506347656</v>
       </c>
       <c r="C203" t="n">
         <v>303.9262084960938</v>
@@ -5826,11 +5838,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>323.3781433105469</v>
+        <v>323.3781127929688</v>
       </c>
       <c r="C204" t="n">
         <v>333.7748413085938</v>
@@ -5855,7 +5867,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5884,11 +5896,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>343.6717224121094</v>
+        <v>343.6717834472656</v>
       </c>
       <c r="C206" t="n">
         <v>354.7209167480469</v>
@@ -5913,11 +5925,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>313.5606689453125</v>
+        <v>313.5606079101562</v>
       </c>
       <c r="C207" t="n">
         <v>322.8003845214844</v>
@@ -5942,11 +5954,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>316.8414001464844</v>
+        <v>316.8414611816406</v>
       </c>
       <c r="C208" t="n">
         <v>326.1778564453125</v>
@@ -5971,11 +5983,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>333.2088317871094</v>
+        <v>333.2087707519531</v>
       </c>
       <c r="C209" t="n">
         <v>343.0274353027344</v>
@@ -6000,11 +6012,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>338.5211791992188</v>
+        <v>338.5212097167969</v>
       </c>
       <c r="C210" t="n">
         <v>347.6159057617188</v>
@@ -6029,11 +6041,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>369.3486328125</v>
+        <v>369.3486022949219</v>
       </c>
       <c r="C211" t="n">
         <v>379.2715148925781</v>
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>363.4705810546875</v>
+        <v>363.4705505371094</v>
       </c>
       <c r="C212" t="n">
         <v>373.2355651855469</v>
@@ -6087,11 +6099,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>360.9471130371094</v>
+        <v>360.9471435546875</v>
       </c>
       <c r="C213" t="n">
         <v>369.7824096679688</v>
@@ -6116,11 +6128,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>337.4448547363281</v>
+        <v>337.4448852539062</v>
       </c>
       <c r="C214" t="n">
         <v>345.704833984375</v>
@@ -6145,11 +6157,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>322.5769653320312</v>
+        <v>322.5769958496094</v>
       </c>
       <c r="C215" t="n">
         <v>330.4730224609375</v>
@@ -6174,11 +6186,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>384.8405151367188</v>
+        <v>384.8405456542969</v>
       </c>
       <c r="C216" t="n">
         <v>393.4058532714844</v>
@@ -6203,11 +6215,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>407.6905212402344</v>
+        <v>407.6905517578125</v>
       </c>
       <c r="C217" t="n">
         <v>416.7644348144531</v>
@@ -6232,11 +6244,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>414.9369812011719</v>
+        <v>414.93701171875</v>
       </c>
       <c r="C218" t="n">
         <v>424.1721801757812</v>
@@ -6261,11 +6273,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>397.2801513671875</v>
+        <v>397.2800903320312</v>
       </c>
       <c r="C219" t="n">
         <v>405.2790832519531</v>
@@ -6290,11 +6302,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>394.5628662109375</v>
+        <v>394.5628967285156</v>
       </c>
       <c r="C220" t="n">
         <v>402.5071105957031</v>
@@ -6319,11 +6331,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>385.6412048339844</v>
+        <v>385.6412353515625</v>
       </c>
       <c r="C221" t="n">
         <v>393.4058532714844</v>
@@ -6348,7 +6360,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6377,11 +6389,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>414.4960632324219</v>
+        <v>414.49609375</v>
       </c>
       <c r="C223" t="n">
         <v>421.9489135742188</v>
@@ -6406,7 +6418,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6435,11 +6447,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>477.8527526855469</v>
+        <v>477.8527221679688</v>
       </c>
       <c r="C225" t="n">
         <v>485.5629272460938</v>
@@ -6464,11 +6476,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>480.9996948242188</v>
+        <v>480.9997253417969</v>
       </c>
       <c r="C226" t="n">
         <v>488.7606506347656</v>
@@ -6493,11 +6505,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>447.2397766113281</v>
+        <v>447.23974609375</v>
       </c>
       <c r="C227" t="n">
         <v>454.4559936523438</v>
@@ -6522,11 +6534,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>487.3355712890625</v>
+        <v>487.3355407714844</v>
       </c>
       <c r="C228" t="n">
         <v>494.3330078125</v>
@@ -6551,11 +6563,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>464.5035095214844</v>
+        <v>464.5034790039062</v>
       </c>
       <c r="C229" t="n">
         <v>471.1731262207031</v>
@@ -6580,11 +6592,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>486.3096008300781</v>
+        <v>486.3095703125</v>
       </c>
       <c r="C230" t="n">
         <v>493.2923278808594</v>
@@ -6609,11 +6621,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>498.7071838378906</v>
+        <v>498.7071228027344</v>
       </c>
       <c r="C231" t="n">
         <v>504.9574279785156</v>
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>474.7500915527344</v>
+        <v>474.7500610351562</v>
       </c>
       <c r="C232" t="n">
         <v>480.7001037597656</v>
@@ -6667,7 +6679,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6696,11 +6708,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>480.089599609375</v>
+        <v>480.0895690917969</v>
       </c>
       <c r="C234" t="n">
         <v>485.2033996582031</v>
@@ -6725,11 +6737,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>493.5975646972656</v>
+        <v>493.5976257324219</v>
       </c>
       <c r="C235" t="n">
         <v>498.8552551269531</v>
@@ -6750,7 +6762,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6775,11 +6787,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>514.2910766601562</v>
+        <v>514.291015625</v>
       </c>
       <c r="C237" t="n">
         <v>518.8646850585938</v>
@@ -6800,11 +6812,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>456.4047241210938</v>
+        <v>456.4046936035156</v>
       </c>
       <c r="C238" t="n">
         <v>460.4635620117188</v>
@@ -6825,7 +6837,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6850,7 +6862,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6875,7 +6887,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6900,7 +6912,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6925,7 +6937,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6954,7 +6966,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6983,7 +6995,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7012,7 +7024,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7041,7 +7053,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7070,7 +7082,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7099,7 +7111,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7128,32 +7140,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>406.5</v>
+        <v>403.25</v>
       </c>
       <c r="C250" t="n">
-        <v>406.5</v>
+        <v>403.25</v>
       </c>
       <c r="D250" t="n">
-        <v>29846200</v>
+        <v>31321600</v>
       </c>
       <c r="E250" t="n">
         <v>15.76616840113529</v>
       </c>
       <c r="F250" t="n">
-        <v>25.78305582291819</v>
+        <v>25.57691823023803</v>
       </c>
       <c r="G250" t="n">
         <v>312872000</v>
       </c>
       <c r="H250" t="n">
-        <v>127182468000</v>
+        <v>126165634000</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09539428264593827</v>
+        <v>0.1001099491165716</v>
       </c>
     </row>
   </sheetData>
@@ -7185,75 +7197,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7289,13 +7301,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7331,13 +7343,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7373,13 +7385,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7415,13 +7427,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7457,13 +7469,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7490,7 +7502,7 @@
       <c r="I7" t="n">
         <v>2.194891201513718</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K7" t="n">
@@ -7503,13 +7515,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7536,7 +7548,7 @@
       <c r="I8" t="n">
         <v>2.317880794701987</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K8" t="n">
@@ -7549,13 +7561,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7582,7 +7594,7 @@
       <c r="I9" t="n">
         <v>2.403027436140019</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K9" t="n">
@@ -7595,13 +7607,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7628,7 +7640,7 @@
       <c r="I10" t="n">
         <v>2.554399243140965</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K10" t="n">
@@ -7641,13 +7653,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7674,7 +7686,7 @@
       <c r="I11" t="n">
         <v>2.526017029328287</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K11" t="n">
@@ -7687,13 +7699,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7720,7 +7732,7 @@
       <c r="I12" t="n">
         <v>2.582781456953642</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="K12" t="n">
@@ -7733,13 +7745,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7766,7 +7778,7 @@
       <c r="I13" t="n">
         <v>2.649006622516556</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="K13" t="n">
@@ -7779,13 +7791,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7812,7 +7824,7 @@
       <c r="I14" t="n">
         <v>2.630085146641438</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="K14" t="n">
@@ -7825,13 +7837,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7858,7 +7870,7 @@
       <c r="I15" t="n">
         <v>2.847682119205298</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="K15" t="n">
@@ -7871,13 +7883,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7904,7 +7916,7 @@
       <c r="I16" t="n">
         <v>2.885525070955534</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="K16" t="n">
@@ -7917,13 +7929,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7950,7 +7962,7 @@
       <c r="I17" t="n">
         <v>2.961210974456007</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="K17" t="n">
@@ -7963,13 +7975,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7996,7 +8008,7 @@
       <c r="I18" t="n">
         <v>2.857142857142857</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K18" t="n">
@@ -8009,13 +8021,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8042,7 +8054,7 @@
       <c r="I19" t="n">
         <v>1.447492904446547</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8055,13 +8067,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8088,7 +8100,7 @@
       <c r="I20" t="n">
         <v>3.491012298959318</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="K20" t="n">
@@ -8101,13 +8113,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8134,7 +8146,7 @@
       <c r="I21" t="n">
         <v>3.632923368022706</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="K21" t="n">
@@ -8147,13 +8159,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41569</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8180,7 +8192,7 @@
       <c r="I22" t="n">
         <v>3.320719016083254</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41569</v>
       </c>
       <c r="K22" t="n">
@@ -8193,13 +8205,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8226,7 +8238,7 @@
       <c r="I23" t="n">
         <v>4.626300851466414</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="K23" t="n">
@@ -8239,13 +8251,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8272,7 +8284,7 @@
       <c r="I24" t="n">
         <v>3.017975402081362</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="K24" t="n">
@@ -8285,13 +8297,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8318,7 +8330,7 @@
       <c r="I25" t="n">
         <v>3.159886471144749</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="K25" t="n">
@@ -8331,13 +8343,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8364,7 +8376,7 @@
       <c r="I26" t="n">
         <v>3.084200567644276</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K26" t="n">
@@ -8377,13 +8389,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8410,7 +8422,7 @@
       <c r="I27" t="n">
         <v>-0.4446546830652789</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="K27" t="n">
@@ -8423,13 +8435,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8456,7 +8468,7 @@
       <c r="I28" t="n">
         <v>-0.2459791863765373</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="K28" t="n">
@@ -8469,13 +8481,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8502,7 +8514,7 @@
       <c r="I29" t="n">
         <v>-0.03784295175023655</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="K29" t="n">
@@ -8515,13 +8527,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8548,7 +8560,7 @@
       <c r="I30" t="n">
         <v>0.1797540208136236</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K30" t="n">
@@ -8561,13 +8573,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8594,7 +8606,7 @@
       <c r="I31" t="n">
         <v>3.982970671712394</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="K31" t="n">
@@ -8607,13 +8619,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8640,7 +8652,7 @@
       <c r="I32" t="n">
         <v>3.982970671712394</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="K32" t="n">
@@ -8653,13 +8665,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8686,7 +8698,7 @@
       <c r="I33" t="n">
         <v>4.13434247871334</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K33" t="n">
@@ -8699,13 +8711,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8732,7 +8744,7 @@
       <c r="I34" t="n">
         <v>6.442762535477768</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K34" t="n">
@@ -8745,13 +8757,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8778,7 +8790,7 @@
       <c r="I35" t="n">
         <v>7.521286660359508</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="K35" t="n">
@@ -8791,13 +8803,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8824,7 +8836,7 @@
       <c r="I36" t="n">
         <v>7.928098391674551</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="K36" t="n">
@@ -8837,13 +8849,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8870,7 +8882,7 @@
       <c r="I37" t="n">
         <v>8.098391674550616</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K37" t="n">
@@ -8883,13 +8895,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8916,7 +8928,7 @@
       <c r="I38" t="n">
         <v>6.442762535477768</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K38" t="n">
@@ -8929,13 +8941,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8962,7 +8974,7 @@
       <c r="I39" t="n">
         <v>5.468306527909178</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="K39" t="n">
@@ -8975,13 +8987,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9008,7 +9020,7 @@
       <c r="I40" t="n">
         <v>5.846736045411543</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K40" t="n">
@@ -9021,13 +9033,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9054,7 +9066,7 @@
       <c r="I41" t="n">
         <v>6.035950804162725</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K41" t="n">
@@ -9067,13 +9079,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9100,7 +9112,7 @@
       <c r="I42" t="n">
         <v>6.357615894039736</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K42" t="n">
@@ -9113,13 +9125,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9146,7 +9158,7 @@
       <c r="I43" t="n">
         <v>7.313150425733207</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="K43" t="n">
@@ -9159,13 +9171,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9192,7 +9204,7 @@
       <c r="I44" t="n">
         <v>7.048249763481552</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K44" t="n">
@@ -9205,13 +9217,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9238,7 +9250,7 @@
       <c r="I45" t="n">
         <v>7.445600756859035</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K45" t="n">
@@ -9251,13 +9263,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9284,7 +9296,7 @@
       <c r="I46" t="n">
         <v>7.965941343424788</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K46" t="n">
@@ -9297,13 +9309,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43871</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9330,7 +9342,7 @@
       <c r="I47" t="n">
         <v>8.126773888363292</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43871</v>
       </c>
       <c r="K47" t="n">
@@ -9343,13 +9355,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9376,7 +9388,7 @@
       <c r="I48" t="n">
         <v>9.044465468306528</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="K48" t="n">
@@ -9389,13 +9401,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9422,7 +9434,7 @@
       <c r="I49" t="n">
         <v>10.02838221381268</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="K49" t="n">
@@ -9435,13 +9447,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9468,7 +9480,7 @@
       <c r="I50" t="n">
         <v>9.441816461684013</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K50" t="n">
@@ -9481,13 +9493,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9514,7 +9526,7 @@
       <c r="I51" t="n">
         <v>9.139072847682119</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="K51" t="n">
@@ -9527,13 +9539,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9560,7 +9572,7 @@
       <c r="I52" t="n">
         <v>9.612109744560076</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9573,13 +9585,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9606,7 +9618,7 @@
       <c r="I53" t="n">
         <v>9.631031220435194</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9619,13 +9631,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9652,7 +9664,7 @@
       <c r="I54" t="n">
         <v>10.97445600756859</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="K54" t="n">
@@ -9665,13 +9677,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44600</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9698,7 +9710,7 @@
       <c r="I55" t="n">
         <v>11.83538315988647</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44600</v>
       </c>
       <c r="K55" t="n">
@@ -9711,13 +9723,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9744,7 +9756,7 @@
       <c r="I56" t="n">
         <v>13.11258278145695</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K56" t="n">
@@ -9757,13 +9769,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9790,7 +9802,7 @@
       <c r="I57" t="n">
         <v>12.69631031220435</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K57" t="n">
@@ -9803,13 +9815,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9836,7 +9848,7 @@
       <c r="I58" t="n">
         <v>11.31504257332072</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K58" t="n">
@@ -9849,13 +9861,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9882,7 +9894,7 @@
       <c r="I59" t="n">
         <v>9.649952696310311</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K59" t="n">
@@ -9895,13 +9907,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9928,7 +9940,7 @@
       <c r="I60" t="n">
         <v>7.757805108798486</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9941,13 +9953,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9974,7 +9986,7 @@
       <c r="I61" t="n">
         <v>6.565752128666036</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -9987,13 +9999,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10020,7 +10032,7 @@
       <c r="I62" t="n">
         <v>7.029328287606433</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K62" t="n">
@@ -10033,13 +10045,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10066,7 +10078,7 @@
       <c r="I63" t="n">
         <v>7.786187322611164</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="K63" t="n">
@@ -10079,13 +10091,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10112,7 +10124,7 @@
       <c r="I64" t="n">
         <v>8.438978240302744</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K64" t="n">
@@ -10125,13 +10137,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10158,7 +10170,7 @@
       <c r="I65" t="n">
         <v>9.981078524124882</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="K65" t="n">
@@ -10171,13 +10183,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10204,7 +10216,7 @@
       <c r="I66" t="n">
         <v>10.71901608325449</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="K66" t="n">
@@ -10217,13 +10229,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10250,7 +10262,7 @@
       <c r="I67" t="n">
         <v>11.68401135288552</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K67" t="n">
@@ -10263,13 +10275,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10296,7 +10308,7 @@
       <c r="I68" t="n">
         <v>12.04351939451277</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K68" t="n">
@@ -10309,13 +10321,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10342,7 +10354,7 @@
       <c r="I69" t="n">
         <v>12.29895931882687</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K69" t="n">
@@ -10355,13 +10367,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10388,7 +10400,7 @@
       <c r="I70" t="n">
         <v>13.0085146641438</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K70" t="n">
@@ -10401,13 +10413,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10434,7 +10446,7 @@
       <c r="I71" t="n">
         <v>13.86944181646168</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K71" t="n">
@@ -10447,13 +10459,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10480,7 +10492,7 @@
       <c r="I72" t="n">
         <v>14.95742667928098</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="K72" t="n">
@@ -10493,13 +10505,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10520,7 +10532,7 @@
       <c r="I73" t="n">
         <v>15.76616840113529</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K73" t="n">
@@ -10557,52 +10569,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40011</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="C2" t="n">
@@ -10631,10 +10643,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40102</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="C3" t="n">
@@ -10663,10 +10675,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="C4" t="n">
@@ -10695,10 +10707,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40284</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="C5" t="n">
@@ -10727,10 +10739,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40375</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="C6" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40466</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="C7" t="n">
@@ -10791,10 +10803,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40585</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="C8" t="n">
@@ -10823,10 +10835,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40648</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="C9" t="n">
@@ -10855,10 +10867,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="C10" t="n">
@@ -10887,10 +10899,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40830</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="C11" t="n">
@@ -10919,10 +10931,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40928</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="C12" t="n">
@@ -10951,10 +10963,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41015</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="C13" t="n">
@@ -10983,10 +10995,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="C14" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41197</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C15" t="n">
@@ -11047,10 +11059,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41383</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="C17" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41474</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="C18" t="n">
@@ -11143,10 +11155,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41565</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41569</v>
       </c>
       <c r="C19" t="n">
@@ -11175,10 +11187,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="C20" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41747</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41758</v>
       </c>
       <c r="C21" t="n">
@@ -11239,10 +11251,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="C22" t="n">
@@ -11271,10 +11283,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41929</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C23" t="n">
@@ -11303,10 +11315,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="C24" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42122</v>
       </c>
       <c r="C25" t="n">
@@ -11367,10 +11379,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42202</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42213</v>
       </c>
       <c r="C26" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42293</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C27" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42391</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="C28" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42486</v>
       </c>
       <c r="C29" t="n">
@@ -11495,10 +11507,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42566</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C30" t="n">
@@ -11527,10 +11539,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C31" t="n">
@@ -11559,10 +11571,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42762</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="C32" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42851</v>
       </c>
       <c r="C33" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C34" t="n">
@@ -11655,10 +11667,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C35" t="n">
@@ -11687,10 +11699,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43126</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="C36" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C37" t="n">
@@ -11751,10 +11763,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C38" t="n">
@@ -11783,10 +11795,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C39" t="n">
@@ -11815,10 +11827,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43490</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="C40" t="n">
@@ -11847,10 +11859,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43581</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C41" t="n">
@@ -11879,10 +11891,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43672</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C42" t="n">
@@ -11911,10 +11923,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C43" t="n">
@@ -11943,10 +11955,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43854</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43871</v>
       </c>
       <c r="C44" t="n">
@@ -11975,10 +11987,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43945</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43949</v>
       </c>
       <c r="C45" t="n">
@@ -12007,10 +12019,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44036</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44040</v>
       </c>
       <c r="C46" t="n">
@@ -12039,10 +12051,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C47" t="n">
@@ -12071,10 +12083,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44232</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44236</v>
       </c>
       <c r="C48" t="n">
@@ -12103,10 +12115,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44309</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C49" t="n">
@@ -12135,10 +12147,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C50" t="n">
@@ -12167,10 +12179,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44491</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="C51" t="n">
@@ -12199,10 +12211,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44596</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44600</v>
       </c>
       <c r="C52" t="n">
@@ -12231,10 +12243,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C54" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44855</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C55" t="n">
@@ -12327,10 +12339,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44953</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C56" t="n">
@@ -12359,10 +12371,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C57" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C58" t="n">
@@ -12423,10 +12435,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12455,10 +12467,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45317</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="C60" t="n">
@@ -12487,10 +12499,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C61" t="n">
@@ -12519,10 +12531,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="C62" t="n">
@@ -12551,10 +12563,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45583</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="C63" t="n">
@@ -12583,10 +12595,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C64" t="n">
@@ -12615,10 +12627,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C65" t="n">
@@ -12647,10 +12659,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C66" t="n">
@@ -12679,10 +12691,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="C67" t="n">
@@ -12711,10 +12723,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="C68" t="n">
@@ -12761,12 +12773,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/SPGI.xlsx
+++ b/salidas/empresas/SPGI.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>33.68464660644531</v>
+        <v>33.68463516235352</v>
       </c>
       <c r="C2" t="n">
         <v>48.28760528564453</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>35.15530014038086</v>
+        <v>35.15529251098633</v>
       </c>
       <c r="C3" t="n">
         <v>50.22705841064453</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>38.15498352050781</v>
+        <v>38.15499114990234</v>
       </c>
       <c r="C4" t="n">
         <v>54.51277160644531</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>36.85709381103516</v>
+        <v>36.85708236694336</v>
       </c>
       <c r="C5" t="n">
         <v>52.65846633911133</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.38042831420898</v>
+        <v>33.38042449951172</v>
       </c>
       <c r="C7" t="n">
         <v>47.52128601074219</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>37.41425704956055</v>
+        <v>37.41424179077148</v>
       </c>
       <c r="C8" t="n">
         <v>53.26395416259766</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>37.27594375610352</v>
+        <v>37.27593231201172</v>
       </c>
       <c r="C9" t="n">
         <v>52.89498519897461</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>38.68937301635742</v>
+        <v>38.68936920166016</v>
       </c>
       <c r="C10" t="n">
         <v>54.90066146850586</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>42.78299713134766</v>
+        <v>42.78300857543945</v>
       </c>
       <c r="C11" t="n">
         <v>60.70955657958984</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>44.55912017822266</v>
+        <v>44.55910873413086</v>
       </c>
       <c r="C12" t="n">
         <v>63.05581665039062</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>45.47502136230469</v>
+        <v>45.47503280639648</v>
       </c>
       <c r="C13" t="n">
         <v>64.35193634033203</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>44.84660339355469</v>
+        <v>44.84659576416016</v>
       </c>
       <c r="C14" t="n">
         <v>63.46263122558594</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>43.29111480712891</v>
+        <v>43.29112243652344</v>
       </c>
       <c r="C15" t="n">
         <v>61.07852554321289</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.16456985473633</v>
+        <v>42.16458129882812</v>
       </c>
       <c r="C16" t="n">
         <v>59.48912048339844</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>43.94157028198242</v>
+        <v>43.94155502319336</v>
       </c>
       <c r="C17" t="n">
         <v>61.9962158203125</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>45.78440856933594</v>
+        <v>45.78440093994141</v>
       </c>
       <c r="C19" t="n">
         <v>64.40870666503906</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>34.07352447509766</v>
+        <v>34.07352828979492</v>
       </c>
       <c r="C21" t="n">
         <v>47.73888397216797</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>34.37738418579102</v>
+        <v>34.37738037109375</v>
       </c>
       <c r="C22" t="n">
         <v>48.16461563110352</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>33.7899055480957</v>
+        <v>33.78992080688477</v>
       </c>
       <c r="C23" t="n">
         <v>47.34153366088867</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>33.28944778442383</v>
+        <v>33.28944396972656</v>
       </c>
       <c r="C24" t="n">
         <v>46.43330383300781</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>29.71497917175293</v>
+        <v>29.7149658203125</v>
       </c>
       <c r="C25" t="n">
         <v>41.44749450683594</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>29.00277137756348</v>
+        <v>29.0028018951416</v>
       </c>
       <c r="C26" t="n">
         <v>40.45411682128906</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>27.91091346740723</v>
+        <v>27.91091537475586</v>
       </c>
       <c r="C27" t="n">
         <v>38.72280120849609</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>25.19687652587891</v>
+        <v>25.19687843322754</v>
       </c>
       <c r="C28" t="n">
         <v>34.95742797851562</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>27.95182418823242</v>
+        <v>27.95181465148926</v>
       </c>
       <c r="C29" t="n">
         <v>38.77956390380859</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>28.44564247131348</v>
+        <v>28.44564056396484</v>
       </c>
       <c r="C30" t="n">
         <v>39.25260162353516</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>27.50636672973633</v>
+        <v>27.50637626647949</v>
       </c>
       <c r="C31" t="n">
         <v>37.95648193359375</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.88345718383789</v>
+        <v>27.88346481323242</v>
       </c>
       <c r="C32" t="n">
         <v>38.47682189941406</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>29.52638244628906</v>
+        <v>29.52639198303223</v>
       </c>
       <c r="C33" t="n">
         <v>40.52980041503906</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>21.78639030456543</v>
+        <v>21.78640365600586</v>
       </c>
       <c r="C34" t="n">
         <v>29.90539360046387</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>18.51258087158203</v>
+        <v>18.5125789642334</v>
       </c>
       <c r="C35" t="n">
         <v>25.41154289245605</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.17453765869141</v>
+        <v>16.1745491027832</v>
       </c>
       <c r="C37" t="n">
         <v>21.93945121765137</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>15.33755970001221</v>
+        <v>15.33756542205811</v>
       </c>
       <c r="C38" t="n">
         <v>20.80416297912598</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>13.90916442871094</v>
+        <v>13.90916347503662</v>
       </c>
       <c r="C39" t="n">
         <v>18.66603660583496</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>16.12278175354004</v>
+        <v>16.12278366088867</v>
       </c>
       <c r="C40" t="n">
         <v>21.6367073059082</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.2549991607666</v>
+        <v>21.25500297546387</v>
       </c>
       <c r="C41" t="n">
         <v>28.52412414550781</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.36922264099121</v>
+        <v>21.36921310424805</v>
       </c>
       <c r="C42" t="n">
         <v>28.46735954284668</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.38342094421387</v>
+        <v>21.38341903686523</v>
       </c>
       <c r="C43" t="n">
         <v>28.48628234863281</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.2640323638916</v>
+        <v>22.26404190063477</v>
       </c>
       <c r="C44" t="n">
         <v>29.6594123840332</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.05143165588379</v>
+        <v>24.05142402648926</v>
       </c>
       <c r="C45" t="n">
         <v>31.79754066467285</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>17.99027442932129</v>
+        <v>17.99027061462402</v>
       </c>
       <c r="C46" t="n">
         <v>23.78429412841797</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>20.59506225585938</v>
+        <v>20.59507179260254</v>
       </c>
       <c r="C47" t="n">
         <v>27.22800445556641</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.59627342224121</v>
+        <v>21.59627914428711</v>
       </c>
       <c r="C48" t="n">
         <v>28.3443717956543</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>24.15524673461914</v>
+        <v>24.15525054931641</v>
       </c>
       <c r="C49" t="n">
         <v>31.70293235778809</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>25.55367660522461</v>
+        <v>25.55366134643555</v>
       </c>
       <c r="C50" t="n">
         <v>33.53831481933594</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.81769561767578</v>
+        <v>24.81770324707031</v>
       </c>
       <c r="C51" t="n">
         <v>32.3557243347168</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>25.86992073059082</v>
+        <v>25.86991119384766</v>
       </c>
       <c r="C52" t="n">
         <v>33.72753143310547</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>24.46938514709473</v>
+        <v>24.46938896179199</v>
       </c>
       <c r="C53" t="n">
         <v>31.90160751342773</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>20.34171485900879</v>
+        <v>20.34171867370605</v>
       </c>
       <c r="C54" t="n">
         <v>26.30085182189941</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>20.59049415588379</v>
+        <v>20.59049224853516</v>
       </c>
       <c r="C55" t="n">
         <v>26.62251663208008</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>22.45637893676758</v>
+        <v>22.45637702941895</v>
       </c>
       <c r="C56" t="n">
         <v>29.03500556945801</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>20.4033260345459</v>
+        <v>20.40331649780273</v>
       </c>
       <c r="C57" t="n">
         <v>26.15893936157227</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>24.39543342590332</v>
+        <v>24.39543151855469</v>
       </c>
       <c r="C58" t="n">
         <v>31.27720069885254</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>27.78246307373047</v>
+        <v>27.78245162963867</v>
       </c>
       <c r="C59" t="n">
         <v>35.61967849731445</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>27.04901313781738</v>
+        <v>27.04901885986328</v>
       </c>
       <c r="C61" t="n">
         <v>34.44654846191406</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>28.95825004577637</v>
+        <v>28.95826530456543</v>
       </c>
       <c r="C62" t="n">
         <v>36.87795639038086</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>28.92151641845703</v>
+        <v>28.92150497436523</v>
       </c>
       <c r="C63" t="n">
         <v>36.59413528442383</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>29.45984840393066</v>
+        <v>29.45986175537109</v>
       </c>
       <c r="C64" t="n">
         <v>37.27530670166016</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>30.25991439819336</v>
+        <v>30.25990867614746</v>
       </c>
       <c r="C65" t="n">
         <v>38.28760528564453</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>31.94393920898438</v>
+        <v>31.94395065307617</v>
       </c>
       <c r="C66" t="n">
         <v>40.17975234985352</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>31.52274894714355</v>
+        <v>31.52273178100586</v>
       </c>
       <c r="C67" t="n">
         <v>39.64995193481445</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>31.28958511352539</v>
+        <v>31.28957557678223</v>
       </c>
       <c r="C68" t="n">
         <v>39.35667037963867</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.87916564941406</v>
+        <v>31.8791561126709</v>
       </c>
       <c r="C69" t="n">
         <v>39.83916854858398</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>31.03883934020996</v>
+        <v>31.03884506225586</v>
       </c>
       <c r="C70" t="n">
         <v>38.78902435302734</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.17441558837891</v>
+        <v>32.17442321777344</v>
       </c>
       <c r="C71" t="n">
         <v>40.20813751220703</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>32.51186752319336</v>
+        <v>32.5118522644043</v>
       </c>
       <c r="C72" t="n">
         <v>40.3973503112793</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>34.24024200439453</v>
+        <v>34.24023056030273</v>
       </c>
       <c r="C73" t="n">
         <v>42.54493713378906</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>35.02447128295898</v>
+        <v>35.02449035644531</v>
       </c>
       <c r="C74" t="n">
         <v>43.51939392089844</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>35.63434219360352</v>
+        <v>35.63434982299805</v>
       </c>
       <c r="C75" t="n">
         <v>44.0302734375</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>37.11208724975586</v>
+        <v>37.11209869384766</v>
       </c>
       <c r="C76" t="n">
         <v>45.85619735717773</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>37.64806747436523</v>
+        <v>37.64805603027344</v>
       </c>
       <c r="C77" t="n">
         <v>46.51844787597656</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>33.40462493896484</v>
+        <v>33.40461349487305</v>
       </c>
       <c r="C78" t="n">
         <v>41.04067993164062</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>34.652099609375</v>
+        <v>34.65209579467773</v>
       </c>
       <c r="C79" t="n">
         <v>42.57332229614258</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>36.16138458251953</v>
+        <v>36.16138076782227</v>
       </c>
       <c r="C80" t="n">
         <v>44.4276237487793</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>39.63051223754883</v>
+        <v>39.63050842285156</v>
       </c>
       <c r="C81" t="n">
         <v>48.4389762878418</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>42.25448226928711</v>
+        <v>42.25447463989258</v>
       </c>
       <c r="C82" t="n">
         <v>51.64616775512695</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>42.78854751586914</v>
+        <v>42.78856658935547</v>
       </c>
       <c r="C83" t="n">
         <v>52.29895782470703</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>41.31171798706055</v>
+        <v>41.31174468994141</v>
       </c>
       <c r="C84" t="n">
         <v>50.24597930908203</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>46.87506484985352</v>
+        <v>46.87506866455078</v>
       </c>
       <c r="C86" t="n">
         <v>54.41816329956055</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>38.1683235168457</v>
+        <v>38.16830825805664</v>
       </c>
       <c r="C87" t="n">
         <v>44.03973388671875</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>42.70259094238281</v>
+        <v>42.70259857177734</v>
       </c>
       <c r="C88" t="n">
         <v>49.27152252197266</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>44.3670768737793</v>
+        <v>44.36708450317383</v>
       </c>
       <c r="C89" t="n">
         <v>51.19205474853516</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.96085357666016</v>
+        <v>44.96086502075195</v>
       </c>
       <c r="C90" t="n">
         <v>51.60832595825195</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>43.83991622924805</v>
+        <v>43.83993530273438</v>
       </c>
       <c r="C91" t="n">
         <v>50.3216667175293</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>48.33486938476562</v>
+        <v>48.33488082885742</v>
       </c>
       <c r="C93" t="n">
         <v>55.22232818603516</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>54.3135986328125</v>
+        <v>54.31360244750977</v>
       </c>
       <c r="C94" t="n">
         <v>62.052978515625</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>57.7004508972168</v>
+        <v>57.70043563842773</v>
       </c>
       <c r="C95" t="n">
         <v>65.92242431640625</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>65.00246429443359</v>
+        <v>65.00241088867188</v>
       </c>
       <c r="C97" t="n">
         <v>73.98297119140625</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>63.20700454711914</v>
+        <v>63.20700073242188</v>
       </c>
       <c r="C98" t="n">
         <v>71.939453125</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>66.464599609375</v>
+        <v>66.46460723876953</v>
       </c>
       <c r="C99" t="n">
         <v>75.36423492431641</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>63.66114807128906</v>
+        <v>63.66119384765625</v>
       </c>
       <c r="C100" t="n">
         <v>72.18543243408203</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>61.68376922607422</v>
+        <v>61.68376541137695</v>
       </c>
       <c r="C101" t="n">
         <v>69.9432373046875</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>68.48304748535156</v>
+        <v>68.48305511474609</v>
       </c>
       <c r="C102" t="n">
         <v>77.36045074462891</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>67.18492126464844</v>
+        <v>67.1849365234375</v>
       </c>
       <c r="C104" t="n">
         <v>75.89404296875</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>68.20455932617188</v>
+        <v>68.20452880859375</v>
       </c>
       <c r="C105" t="n">
         <v>76.75496673583984</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.99560546875</v>
+        <v>70.99562072753906</v>
       </c>
       <c r="C106" t="n">
         <v>79.89593505859375</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>76.06491088867188</v>
+        <v>76.06488800048828</v>
       </c>
       <c r="C107" t="n">
         <v>85.60075378417969</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>78.83036804199219</v>
+        <v>78.83037567138672</v>
       </c>
       <c r="C108" t="n">
         <v>88.42005920410156</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>75.05166625976562</v>
+        <v>75.05164337158203</v>
       </c>
       <c r="C109" t="n">
         <v>84.18164825439453</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>75.43965911865234</v>
+        <v>75.43966674804688</v>
       </c>
       <c r="C110" t="n">
         <v>84.61683654785156</v>
@@ -3190,7 +3190,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>87.49036407470703</v>
+        <v>87.49038696289062</v>
       </c>
       <c r="C112" t="n">
         <v>97.82402801513672</v>
@@ -3217,7 +3217,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>88.25194549560547</v>
+        <v>88.25191497802734</v>
       </c>
       <c r="C113" t="n">
         <v>98.67549896240234</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>88.05843353271484</v>
+        <v>88.0584716796875</v>
       </c>
       <c r="C114" t="n">
         <v>98.15515899658203</v>
@@ -3271,7 +3271,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>85.25759124755859</v>
+        <v>85.25757598876953</v>
       </c>
       <c r="C115" t="n">
         <v>95.03311157226562</v>
@@ -3298,7 +3298,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>86.36094665527344</v>
+        <v>86.36093139648438</v>
       </c>
       <c r="C116" t="n">
         <v>96.26300811767578</v>
@@ -3325,7 +3325,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>82.60338592529297</v>
+        <v>82.60340118408203</v>
       </c>
       <c r="C117" t="n">
         <v>91.75969696044922</v>
@@ -3352,7 +3352,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>73.66935729980469</v>
+        <v>73.66938018798828</v>
       </c>
       <c r="C118" t="n">
         <v>81.83538055419922</v>
@@ -3379,7 +3379,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>78.89864349365234</v>
+        <v>78.89863586425781</v>
       </c>
       <c r="C119" t="n">
         <v>87.64427947998047</v>
@@ -3406,7 +3406,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>82.44129180908203</v>
+        <v>82.44130706787109</v>
       </c>
       <c r="C120" t="n">
         <v>91.26773834228516</v>
@@ -3435,7 +3435,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>84.24446868896484</v>
+        <v>84.24444580078125</v>
       </c>
       <c r="C121" t="n">
         <v>93.26395416259766</v>
@@ -3464,7 +3464,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>72.65638732910156</v>
+        <v>72.65639495849609</v>
       </c>
       <c r="C122" t="n">
         <v>80.43519592285156</v>
@@ -3493,7 +3493,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>76.99989318847656</v>
+        <v>76.99990081787109</v>
       </c>
       <c r="C123" t="n">
         <v>84.90066528320312</v>
@@ -3522,7 +3522,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>84.92810821533203</v>
+        <v>84.92814636230469</v>
       </c>
       <c r="C124" t="n">
         <v>93.64238739013672</v>
@@ -3638,7 +3638,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>105.1996231079102</v>
+        <v>105.1996002197266</v>
       </c>
       <c r="C128" t="n">
         <v>115.6102142333984</v>
@@ -3667,7 +3667,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>106.6698455810547</v>
+        <v>106.6698684692383</v>
       </c>
       <c r="C129" t="n">
         <v>116.8779525756836</v>
@@ -3696,7 +3696,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>109.277458190918</v>
+        <v>109.2774658203125</v>
       </c>
       <c r="C130" t="n">
         <v>119.7350997924805</v>
@@ -3725,7 +3725,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>105.2106399536133</v>
+        <v>105.2106246948242</v>
       </c>
       <c r="C131" t="n">
         <v>115.2790908813477</v>
@@ -3783,7 +3783,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>93.13227081298828</v>
+        <v>93.13229370117188</v>
       </c>
       <c r="C133" t="n">
         <v>101.7407760620117</v>
@@ -3812,7 +3812,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>104.0788421630859</v>
+        <v>104.0788116455078</v>
       </c>
       <c r="C134" t="n">
         <v>113.6991500854492</v>
@@ -3841,7 +3841,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>112.4768753051758</v>
+        <v>112.4768600463867</v>
       </c>
       <c r="C135" t="n">
         <v>122.4881744384766</v>
@@ -3870,7 +3870,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>113.5801696777344</v>
+        <v>113.5801544189453</v>
       </c>
       <c r="C136" t="n">
         <v>123.6896896362305</v>
@@ -3899,7 +3899,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>116.5773696899414</v>
+        <v>116.5773620605469</v>
       </c>
       <c r="C137" t="n">
         <v>126.9536437988281</v>
@@ -3928,7 +3928,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>124.4351272583008</v>
+        <v>124.4351348876953</v>
       </c>
       <c r="C138" t="n">
         <v>135.1087951660156</v>
@@ -3957,7 +3957,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>127.2059097290039</v>
+        <v>127.2059783935547</v>
       </c>
       <c r="C139" t="n">
         <v>138.1173095703125</v>
@@ -3986,7 +3986,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>133.8280944824219</v>
+        <v>133.8281402587891</v>
       </c>
       <c r="C140" t="n">
         <v>145.3074798583984</v>
@@ -4015,7 +4015,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>134.8382568359375</v>
+        <v>134.8383178710938</v>
       </c>
       <c r="C141" t="n">
         <v>146.007568359375</v>
@@ -4044,7 +4044,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>136.5682678222656</v>
+        <v>136.5682373046875</v>
       </c>
       <c r="C142" t="n">
         <v>147.8807983398438</v>
@@ -4073,7 +4073,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>136.7080230712891</v>
+        <v>136.7079925537109</v>
       </c>
       <c r="C143" t="n">
         <v>148.0321655273438</v>
@@ -4102,7 +4102,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>144.9421234130859</v>
+        <v>144.9421539306641</v>
       </c>
       <c r="C144" t="n">
         <v>156.5562896728516</v>
@@ -4131,7 +4131,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>148.3755798339844</v>
+        <v>148.3755950927734</v>
       </c>
       <c r="C145" t="n">
         <v>160.2649078369141</v>
@@ -4160,7 +4160,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>158.6234893798828</v>
+        <v>158.6234741210938</v>
       </c>
       <c r="C146" t="n">
         <v>171.3339691162109</v>
@@ -4189,7 +4189,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>168.4438934326172</v>
+        <v>168.4438323974609</v>
       </c>
       <c r="C147" t="n">
         <v>181.4569549560547</v>
@@ -4218,7 +4218,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>167.7939910888672</v>
+        <v>167.7939758300781</v>
       </c>
       <c r="C148" t="n">
         <v>180.7568664550781</v>
@@ -4276,7 +4276,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>173.8848876953125</v>
+        <v>173.8849334716797</v>
       </c>
       <c r="C150" t="n">
         <v>186.8495788574219</v>
@@ -4305,7 +4305,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>179.5108032226562</v>
+        <v>179.5108184814453</v>
       </c>
       <c r="C151" t="n">
         <v>192.8949890136719</v>
@@ -4334,7 +4334,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>176.4733581542969</v>
+        <v>176.4732971191406</v>
       </c>
       <c r="C152" t="n">
         <v>189.6310272216797</v>
@@ -4421,7 +4421,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>160.9166412353516</v>
+        <v>160.9165954589844</v>
       </c>
       <c r="C155" t="n">
         <v>172.4881744384766</v>
@@ -4450,7 +4450,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>161.8492889404297</v>
+        <v>161.8493804931641</v>
       </c>
       <c r="C156" t="n">
         <v>172.9990539550781</v>
@@ -4479,7 +4479,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>150.413818359375</v>
+        <v>150.4138488769531</v>
       </c>
       <c r="C157" t="n">
         <v>160.7757873535156</v>
@@ -4537,7 +4537,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>177.849609375</v>
+        <v>177.8496246337891</v>
       </c>
       <c r="C159" t="n">
         <v>189.5648040771484</v>
@@ -4566,7 +4566,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>186.8854064941406</v>
+        <v>186.8854217529297</v>
       </c>
       <c r="C160" t="n">
         <v>199.1958312988281</v>
@@ -4595,7 +4595,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>195.8591613769531</v>
+        <v>195.8591156005859</v>
       </c>
       <c r="C161" t="n">
         <v>208.7606353759766</v>
@@ -4624,7 +4624,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>190.3473968505859</v>
+        <v>190.347412109375</v>
       </c>
       <c r="C162" t="n">
         <v>202.3462677001953</v>
@@ -4653,7 +4653,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>202.7269134521484</v>
+        <v>202.7268981933594</v>
       </c>
       <c r="C163" t="n">
         <v>215.5061492919922</v>
@@ -4682,7 +4682,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>217.9988555908203</v>
+        <v>217.9988708496094</v>
       </c>
       <c r="C164" t="n">
         <v>231.7407684326172</v>
@@ -4711,7 +4711,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>232.0766296386719</v>
+        <v>232.07666015625</v>
       </c>
       <c r="C165" t="n">
         <v>246.158935546875</v>
@@ -4740,7 +4740,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>218.5101165771484</v>
+        <v>218.5101318359375</v>
       </c>
       <c r="C166" t="n">
         <v>231.7691650390625</v>
@@ -4769,7 +4769,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>230.1143646240234</v>
+        <v>230.1143493652344</v>
       </c>
       <c r="C167" t="n">
         <v>244.0775756835938</v>
@@ -4798,7 +4798,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>236.5632171630859</v>
+        <v>236.5631713867188</v>
       </c>
       <c r="C168" t="n">
         <v>250.3784332275391</v>
@@ -4827,7 +4827,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>244.0717163085938</v>
+        <v>244.0716857910156</v>
       </c>
       <c r="C169" t="n">
         <v>258.325439453125</v>
@@ -4856,7 +4856,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>262.5569152832031</v>
+        <v>262.5570068359375</v>
       </c>
       <c r="C170" t="n">
         <v>277.8902587890625</v>
@@ -4885,7 +4885,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>238.2382049560547</v>
+        <v>238.2381591796875</v>
       </c>
       <c r="C171" t="n">
         <v>251.5704803466797</v>
@@ -4914,7 +4914,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>219.5489959716797</v>
+        <v>219.5489807128906</v>
       </c>
       <c r="C172" t="n">
         <v>231.8353881835938</v>
@@ -4943,7 +4943,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>262.4015808105469</v>
+        <v>262.401611328125</v>
       </c>
       <c r="C173" t="n">
         <v>277.0860900878906</v>
@@ -4972,7 +4972,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>291.8238525390625</v>
+        <v>291.8238220214844</v>
       </c>
       <c r="C174" t="n">
         <v>307.4928894042969</v>
@@ -5059,7 +5059,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>329.60888671875</v>
+        <v>329.6089477539062</v>
       </c>
       <c r="C177" t="n">
         <v>346.6603698730469</v>
@@ -5117,7 +5117,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>290.3080444335938</v>
+        <v>290.3079528808594</v>
       </c>
       <c r="C179" t="n">
         <v>305.3263854980469</v>
@@ -5146,7 +5146,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>317.0697631835938</v>
+        <v>317.06982421875</v>
       </c>
       <c r="C180" t="n">
         <v>332.8098449707031</v>
@@ -5204,7 +5204,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>285.7215576171875</v>
+        <v>285.7215270996094</v>
       </c>
       <c r="C182" t="n">
         <v>299.9053955078125</v>
@@ -5233,7 +5233,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>297.5494689941406</v>
+        <v>297.5494079589844</v>
       </c>
       <c r="C183" t="n">
         <v>311.598876953125</v>
@@ -5262,7 +5262,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>318.7887573242188</v>
+        <v>318.7887878417969</v>
       </c>
       <c r="C184" t="n">
         <v>333.841064453125</v>
@@ -5320,7 +5320,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>343.5174865722656</v>
+        <v>343.5174255371094</v>
       </c>
       <c r="C186" t="n">
         <v>359.0066223144531</v>
@@ -5349,7 +5349,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>371.5623168945312</v>
+        <v>371.5622863769531</v>
       </c>
       <c r="C187" t="n">
         <v>388.3159790039062</v>
@@ -5378,7 +5378,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>388.1012573242188</v>
+        <v>388.101318359375</v>
       </c>
       <c r="C188" t="n">
         <v>405.6007690429688</v>
@@ -5407,7 +5407,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>402.4788208007812</v>
+        <v>402.4788818359375</v>
       </c>
       <c r="C189" t="n">
         <v>419.886474609375</v>
@@ -5465,7 +5465,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>429.9927978515625</v>
+        <v>429.9927368164062</v>
       </c>
       <c r="C191" t="n">
         <v>448.5903625488281</v>
@@ -5494,7 +5494,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>413.9749450683594</v>
+        <v>413.9748840332031</v>
       </c>
       <c r="C192" t="n">
         <v>431.1542053222656</v>
@@ -5552,7 +5552,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>377.1765441894531</v>
+        <v>377.1764831542969</v>
       </c>
       <c r="C194" t="n">
         <v>392.8287658691406</v>
@@ -5581,7 +5581,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>341.9359741210938</v>
+        <v>341.93603515625</v>
       </c>
       <c r="C195" t="n">
         <v>355.4399108886719</v>
@@ -5610,7 +5610,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>373.3172912597656</v>
+        <v>373.3173522949219</v>
       </c>
       <c r="C196" t="n">
         <v>388.060546875</v>
@@ -5639,7 +5639,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>342.6641540527344</v>
+        <v>342.6640930175781</v>
       </c>
       <c r="C197" t="n">
         <v>356.19677734375</v>
@@ -5668,7 +5668,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>318.8519592285156</v>
+        <v>318.8520202636719</v>
       </c>
       <c r="C198" t="n">
         <v>330.6338806152344</v>
@@ -5697,7 +5697,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>307.5204162597656</v>
+        <v>307.5205383300781</v>
       </c>
       <c r="C199" t="n">
         <v>318.8836364746094</v>
@@ -5755,7 +5755,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>322.0439147949219</v>
+        <v>322.0439758300781</v>
       </c>
       <c r="C201" t="n">
         <v>333.1882629394531</v>
@@ -5871,7 +5871,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>307.0075378417969</v>
+        <v>307.007568359375</v>
       </c>
       <c r="C205" t="n">
         <v>316.8779602050781</v>
@@ -5900,7 +5900,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>343.6717834472656</v>
+        <v>343.6717529296875</v>
       </c>
       <c r="C206" t="n">
         <v>354.7209167480469</v>
@@ -5987,7 +5987,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>333.2087707519531</v>
+        <v>333.2087097167969</v>
       </c>
       <c r="C209" t="n">
         <v>343.0274353027344</v>
@@ -6045,7 +6045,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>369.3486022949219</v>
+        <v>369.3485717773438</v>
       </c>
       <c r="C211" t="n">
         <v>379.2715148925781</v>
@@ -6074,7 +6074,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>363.4705505371094</v>
+        <v>363.4705200195312</v>
       </c>
       <c r="C212" t="n">
         <v>373.2355651855469</v>
@@ -6103,7 +6103,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>360.9471435546875</v>
+        <v>360.9471740722656</v>
       </c>
       <c r="C213" t="n">
         <v>369.7824096679688</v>
@@ -6132,7 +6132,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>337.4448852539062</v>
+        <v>337.4449157714844</v>
       </c>
       <c r="C214" t="n">
         <v>345.704833984375</v>
@@ -6161,7 +6161,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>322.5769958496094</v>
+        <v>322.576904296875</v>
       </c>
       <c r="C215" t="n">
         <v>330.4730224609375</v>
@@ -6248,7 +6248,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>414.93701171875</v>
+        <v>414.9370422363281</v>
       </c>
       <c r="C218" t="n">
         <v>424.1721801757812</v>
@@ -6277,7 +6277,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>397.2800903320312</v>
+        <v>397.2801513671875</v>
       </c>
       <c r="C219" t="n">
         <v>405.2790832519531</v>
@@ -6306,7 +6306,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>394.5628967285156</v>
+        <v>394.5628662109375</v>
       </c>
       <c r="C220" t="n">
         <v>402.5071105957031</v>
@@ -6335,7 +6335,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>385.6412353515625</v>
+        <v>385.6412658691406</v>
       </c>
       <c r="C221" t="n">
         <v>393.4058532714844</v>
@@ -6364,7 +6364,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>397.3121643066406</v>
+        <v>397.3121948242188</v>
       </c>
       <c r="C222" t="n">
         <v>404.4559936523438</v>
@@ -6422,7 +6422,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>450.4903869628906</v>
+        <v>450.4902954101562</v>
       </c>
       <c r="C224" t="n">
         <v>458.5903625488281</v>
@@ -6480,7 +6480,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>480.9997253417969</v>
+        <v>480.9996948242188</v>
       </c>
       <c r="C226" t="n">
         <v>488.7606506347656</v>
@@ -6567,7 +6567,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>464.5034790039062</v>
+        <v>464.5035095214844</v>
       </c>
       <c r="C229" t="n">
         <v>471.1731262207031</v>
@@ -6596,7 +6596,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>486.3095703125</v>
+        <v>486.3096008300781</v>
       </c>
       <c r="C230" t="n">
         <v>493.2923278808594</v>
@@ -6683,7 +6683,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>467.2284545898438</v>
+        <v>467.2284240722656</v>
       </c>
       <c r="C233" t="n">
         <v>473.0841979980469</v>
@@ -6712,7 +6712,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>480.0895690917969</v>
+        <v>480.0896301269531</v>
       </c>
       <c r="C234" t="n">
         <v>485.2033996582031</v>
@@ -6741,7 +6741,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>493.5976257324219</v>
+        <v>493.5975646972656</v>
       </c>
       <c r="C235" t="n">
         <v>498.8552551269531</v>
@@ -6791,7 +6791,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>514.291015625</v>
+        <v>514.2910766601562</v>
       </c>
       <c r="C237" t="n">
         <v>518.8646850585938</v>
@@ -6816,7 +6816,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>456.4046936035156</v>
+        <v>456.4047241210938</v>
       </c>
       <c r="C238" t="n">
         <v>460.4635620117188</v>
